--- a/data/seed/portfolio/L-2024-7443/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-7443/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,23 +540,23 @@
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>154515000</v>
-      </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n">
+        <v>346637000</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Namangan Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>294163528</t>
+          <t>337785570</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000654959719001</t>
+          <t>20208000689055904001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №268/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1815 01.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>658585000</v>
+        <v>1159737000</v>
       </c>
     </row>
     <row r="9">
@@ -580,103 +580,103 @@
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>291451000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>117398000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>211538321</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000644053308001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №291/26 от 01.07.2026, НДС 12%</t>
+          <t>SHARTNOMA №156/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>367134000</v>
+        <v>1277135000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>48012000</v>
+        <v>75119000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Barakali Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6764 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartn. №111/26, QQS 12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>415146000</v>
+        <v>1352254000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>395392000</v>
+        <v>36115000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ishonch Plastik XK</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>392906371</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000207961798001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -686,11 +686,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №213/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8977 03.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>810538000</v>
+        <v>1388369000</v>
       </c>
     </row>
     <row r="12">
@@ -702,35 +702,35 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>116045000</v>
+        <v>51585000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Farovon Ip-Kalava MChJ</t>
+          <t>Barakali Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>302586059</t>
+          <t>221586923</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000787315931001</t>
+          <t>20208000538820846001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5214 06.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2280</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>926583000</v>
+        <v>1439954000</v>
       </c>
     </row>
     <row r="13">
@@ -740,37 +740,37 @@
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>81268000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>84480000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №155/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №62/26</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1007851000</v>
+        <v>1355474000</v>
       </c>
     </row>
     <row r="14">
@@ -780,37 +780,37 @@
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>68035000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>125141000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Shodlik Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>391344936</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000287406485001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6792 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №62/26</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1075886000</v>
+        <v>1230333000</v>
       </c>
     </row>
     <row r="15">
@@ -820,72 +820,72 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>54754000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>160866000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>387662098</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5077 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Iyun oyi uchun ish haqi, reestr №6436</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1130640000</v>
+        <v>1069467000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>160866000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>46596000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Shahrisabz Yog'och XK</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5532</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>969774000</v>
+        <v>1116063000</v>
       </c>
     </row>
     <row r="17">
@@ -901,57 +901,57 @@
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Denov Qurilish MChJ</t>
+          <t>Olmaliq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>319956591</t>
+          <t>368763789</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000954561008001</t>
+          <t>20208000417526975001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по дог. №90/22</t>
+          <t>Аренда помещения за июль, дог. №13/22</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>952614000</v>
+        <v>1098903000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>207715000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>211798000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Andijon Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>388677105</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000017094766001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -961,437 +961,432 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2236</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №197</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>744899000</v>
+        <v>1310701000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>65814000</v>
+        <v>53481000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Farovon Ip-Kalava MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>302586059</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000787315931001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №10/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2602</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>810713000</v>
+        <v>1364182000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>245038000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>82277000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5223 от 10.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №293/26</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1055751000</v>
+        <v>1281905000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>34353000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>98102000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Shodlik Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>391344936</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000287406485001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №4927 ОТ 10.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №181/26</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1090104000</v>
+        <v>1183803000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>118552000</v>
+        <v>757426000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1754</t>
+          <t>Оплата за товары согласно счет-фактуре №7099</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>971552000</v>
+        <v>426377000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>65103000</v>
+        <v>106782000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Barakali Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2816 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товар по счет-фактуре №5567 от 14.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1036655000</v>
+        <v>533159000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>35446000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>21936000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Namangan Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>325377855</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000036890559001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yetkazilgan tvar uchun to'lov h/f №7881</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1072101000</v>
+        <v>511223000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>29680000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>21936000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Namangan Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>325377855</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000036890559001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №199/26, НДС 12%</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1101781000</v>
+        <v>489287000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>21936000</v>
+        <v>180300000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7443)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000372315655417</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Уплата социального нлога за июнь</t>
+          <t>Kredit shartnomasi L-2024-7443 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1079845000</v>
+        <v>308987000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>21936000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>735526000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6628</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1057909000</v>
+        <v>1044513000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>126648000</v>
+        <v>57377000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Barakali Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>221586923</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000538820846001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2982 от 15.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №271/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1184557000</v>
+        <v>1101890000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>87855000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>65010000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1401,72 +1396,77 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №231/26 от 15.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7873</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1096702000</v>
+        <v>1166900000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>180300000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>57780000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7443)</t>
+          <t>Shahrisabz Yog'och XK</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>16307000372315655417</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7443 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №390</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>916402000</v>
+        <v>1224680000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>34648000</v>
+        <v>51215000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №193/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №127/26, QQS 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>951050000</v>
+        <v>1275895000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>203972000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>35290000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Andijon Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>388677105</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000017094766001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1516,117 +1516,117 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №159/26</t>
+          <t>Оплата по счет-фактуре №909 за поставленный товар</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>747078000</v>
+        <v>1311185000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>104172000</v>
+        <v>71954000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tong Ip-Kalava MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>360721766</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000575634495001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата затовар по с/ф №3090 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3442 22.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>851250000</v>
+        <v>1383139000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>209995000</v>
+        <v>66846000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5165 20.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, h/f №1845 22.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1061245000</v>
+        <v>1449985000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>35896000</v>
+        <v>37193000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>361215869</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1636,157 +1636,157 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9750 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9116</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1097141000</v>
+        <v>1487178000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>81355000</v>
+        <v>28652000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1322</t>
+          <t>QQS iyun 2026 uchun</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1015786000</v>
+        <v>1458526000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>94160000</v>
+        <v>207143000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Gulshan Tikuv XK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>372941021</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000028894586001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3599</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №104/26, QQS bilan</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>921626000</v>
+        <v>1251383000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>103978000</v>
+        <v>260541000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №109/26</t>
+          <t>Tovarlar uchun to'lov h/f №69</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>817648000</v>
+        <v>990842000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>276373000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>56310000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1796,56 +1796,56 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №6571</t>
+          <t>Shartnoma №204/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>541275000</v>
+        <v>1047152000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>29650000</v>
+        <v>48118000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №61/26</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>511625000</v>
+        <v>999034000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000523322308001</t>
+          <t>20208000785404252001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1880,47 +1880,47 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>500900000</v>
+        <v>988309000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>97705000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>301063000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shodlik Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>391344936</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000287406485001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2223 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №292/26</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>598605000</v>
+        <v>687246000</v>
       </c>
     </row>
     <row r="43">
@@ -1932,21 +1932,21 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>94040000</v>
+        <v>107661000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>361215869</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1956,392 +1956,387 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9469 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8338</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>692645000</v>
+        <v>794907000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>68410000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>387662098</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №211/26, QQS 12%</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>761055000</v>
+        <v>794607000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>250315000</v>
+        <v>52623000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Ishonch Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>253832106</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000405330890001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №119/26</t>
+          <t>Tovarlar uchun to'lov h/f №1116</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>510740000</v>
+        <v>741984000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>30665000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>90931000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shodlik Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>391344936</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000287406485001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9572 от 28.07.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №100/26, QQS bilan</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>541405000</v>
+        <v>651053000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>336766000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>286385000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №189/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №8800</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>878171000</v>
+        <v>364668000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>59305000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>148404000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>361215869</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №113/26 от 30.07.2026</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>937476000</v>
+        <v>216264000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>33639000</v>
+        <v>43997000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Barakali Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №254/26 от 30.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>971115000</v>
+        <v>260261000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>118312000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>32436000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>294163528</t>
+          <t>204144528</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000654959719001</t>
+          <t>20208000867143835001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №89/26</t>
+          <t>Оплата за продукцию по договору №214/26, НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>852803000</v>
+        <v>292697000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>300000</v>
+        <v>117511000</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Ishonch Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>253832106</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000405330890001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата за упаковочные материалы, с/ф №7588</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>852503000</v>
+        <v>175186000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>22633000</v>
+        <v>104958000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Barakali Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8472 ОТ 03.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2796</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>875136000</v>
+        <v>280144000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>28132000</v>
+        <v>43943000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ishonch Plastik XK</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>392906371</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000207961798001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2351,232 +2346,237 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №128/26 от 04.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9992</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>903268000</v>
+        <v>324087000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>148404000</v>
+        <v>15830000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Olmaliq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>368763789</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000417526975001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>754864000</v>
+        <v>308257000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>73957000</v>
+        <v>370726000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Barakali Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7528 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №978</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>828821000</v>
+        <v>678983000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>180528000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>42160000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>294163528</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000654959719001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4248</t>
+          <t>Tovar uchun to'lov, h/f №111 11.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>648293000</v>
+        <v>721143000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>15830000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>30171000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Denov Qurilish MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>319956591</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000954561008001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №90/22</t>
+          <t>Shartnoma №240/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>632463000</v>
+        <v>751314000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>28031000</v>
+        <v>26068000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №101/26 от 10.08.2026</t>
+          <t>Оплата за продукцию по договору №148/26, НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>660494000</v>
+        <v>777382000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>72737000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>159298000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz XK</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>348398600</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000005134011001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2586,37 +2586,37 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №287/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №87/26 от 12.08.2026</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>587757000</v>
+        <v>936680000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>155346000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>81341000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2626,166 +2626,166 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №36/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №218/26, QQS 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>432411000</v>
+        <v>1018021000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>18225000</v>
+        <v>68290000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №766 за поставленный товар</t>
+          <t>Предоплата за товар по договору №298/26 от 12.08.2026</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>450636000</v>
+        <v>1086311000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>40350000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>180300000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>387662098</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7443)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>16307000372315655417</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3571 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2024-7443 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>490986000</v>
+        <v>906011000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>29313000</v>
+        <v>49925000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Mehnat Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>266758425</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000429934490001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №231/26 от 14.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №9445 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>520299000</v>
+        <v>955936000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>180300000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>39724000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7443)</t>
+          <t>Barakali Ip-Kalava MChJ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>221586923</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>16307000372315655417</t>
+          <t>20208000538820846001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7443 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за товар по дог. №179/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>339999000</v>
+        <v>995660000</v>
       </c>
     </row>
     <row r="65">
@@ -2797,35 +2797,35 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>671047000</v>
+        <v>39364000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №93/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №1914 17.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1011046000</v>
+        <v>1035024000</v>
       </c>
     </row>
     <row r="66">
@@ -2835,37 +2835,37 @@
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>36827000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>20237000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/ №2372</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1047873000</v>
+        <v>1014787000</v>
       </c>
     </row>
     <row r="67">
@@ -2875,37 +2875,37 @@
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>36162000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>20237000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4581 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1084035000</v>
+        <v>994550000</v>
       </c>
     </row>
     <row r="68">
@@ -2915,37 +2915,37 @@
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>22783000</v>
-      </c>
+      <c r="C68" s="2" t="n">
+        <v>37505000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>361215869</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8414 17.08.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №33/26</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1106818000</v>
+        <v>957045000</v>
       </c>
     </row>
     <row r="69">
@@ -2955,37 +2955,37 @@
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>17749000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>52417000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ishonch Plastik XK</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>392906371</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000207961798001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №34/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №77/26</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1124567000</v>
+        <v>904628000</v>
       </c>
     </row>
     <row r="70">
@@ -2996,102 +2996,102 @@
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>20237000</v>
+        <v>53016000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>253832106</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000405330890001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Уплата социального налога заиюль</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №215/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1104330000</v>
+        <v>851612000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>20237000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>289519000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navro'z Tekstil MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>313028976</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000671613337001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Tovar uchun to'lov, h/f №1475 19.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1084093000</v>
+        <v>1141131000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>71953000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>106924000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3101,91 +3101,91 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №212/26, QQS BILAN</t>
+          <t>Предоплата за товар по договору №272/26 от 19.08.2026</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1012140000</v>
+        <v>1248055000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>26904000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>358271000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №253/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №156/26, QQS bilan</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1039044000</v>
+        <v>889784000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>103755000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>52042000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Nukus Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>290637122</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000796179819001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №42/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2271</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>935289000</v>
+        <v>941826000</v>
       </c>
     </row>
     <row r="75">
@@ -3197,75 +3197,75 @@
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>872095000</v>
+        <v>96960000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5618 от 21.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №160/26, НДС 12%</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1807384000</v>
+        <v>1038786000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>27491000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>26603000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>361215869</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1838 за поставленный товар</t>
+          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1834875000</v>
+        <v>1012183000</v>
       </c>
     </row>
     <row r="77">
@@ -3275,37 +3275,37 @@
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>26478000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>54264000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>204144528</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000867143835001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Shartnoma №289/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1808397000</v>
+        <v>1066447000</v>
       </c>
     </row>
     <row r="78">
@@ -3315,37 +3315,37 @@
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>72323000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>43744000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bunyodkor Non MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>388513325</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000936873944001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3882</t>
+          <t>Оплата за товар по счет-фактуре №8550 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1736074000</v>
+        <v>1110191000</v>
       </c>
     </row>
     <row r="79">
@@ -3355,23 +3355,23 @@
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>145388000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>37001000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3381,11 +3381,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4456</t>
+          <t>Shartnoma №16/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1590686000</v>
+        <v>1147192000</v>
       </c>
     </row>
     <row r="80">
@@ -3395,23 +3395,23 @@
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>152365000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>36157000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3421,237 +3421,237 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4769</t>
+          <t>Mahsulot uchun to'lov, shartnoma №70/26, QQS 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1438321000</v>
+        <v>1183349000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>115084000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>36589000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №124/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №7444</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1553405000</v>
+        <v>1146760000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>9894000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>91178000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ishonch Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>204144528</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000523322308001</t>
+          <t>20208000867143835001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Mahsulot uchun to'lov, shartnoma №5/26, QQS 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1543511000</v>
+        <v>1237938000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>74440000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>151230000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bunyodkor Sut MChJ</t>
+          <t>Shodlik Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>240791571</t>
+          <t>391344936</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000080475967001</t>
+          <t>20208000287406485001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9183 от 27.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №1588</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1617951000</v>
+        <v>1086708000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>30086000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>9894000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000785404252001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8413 от 27.08.2026, в т.ч. НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1648037000</v>
+        <v>1076814000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>35217000</v>
+        <v>207935000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
+          <t>Barakali Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>361215869</t>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3780 от 28.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №4007 за поставленный товар</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1683254000</v>
+        <v>1284749000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>306381000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>39826000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Andijon Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>388677105</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000017094766001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3661,51 +3661,51 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №44/26</t>
+          <t>Shartnoma №125/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1376873000</v>
+        <v>1324575000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>460402000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>28945000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>211538321</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000644053308001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8967</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №813</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>916471000</v>
+        <v>1353520000</v>
       </c>
     </row>
     <row r="88">
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>916171000</v>
+        <v>1353220000</v>
       </c>
     </row>
     <row r="89">
@@ -3751,222 +3751,222 @@
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>89141000</v>
+        <v>47174000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Buxoro Non AJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>216352846</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000495971938001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №274/26</t>
+          <t>Tovarlar uchun to'lov h/f №4802</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>827030000</v>
+        <v>1306046000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>23621000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>56442000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Shartnoma №268/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №81/26, QQS bilan</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>850651000</v>
+        <v>1249604000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>104764000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>80781000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>361215869</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №59/26 от 02.09.2026</t>
+          <t>Tovarlar uchun to'lov h/f №864</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>955415000</v>
+        <v>1168823000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>15720000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>367356000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №257/26 от 02.09.2026</t>
+          <t>Оплата за транспортныеуслуги по дог. №172/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>971135000</v>
+        <v>801467000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>52842000</v>
+        <v>299294000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>211538321</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000644053308001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №60/26 ОТ 02.09.2026, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №72/26</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>918293000</v>
+        <v>502173000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>701534000</v>
+        <v>290747000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Barakali Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>221586923</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000538820846001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3976,392 +3976,397 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №642 от 04.09.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №275/26, QQS 12%</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1619827000</v>
+        <v>792920000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>18858000</v>
+        <v>33351000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Barakali Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>221586923</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000538820846001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №208/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5852 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1638685000</v>
+        <v>826271000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>16342000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>144827000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tong Ip-Kalava MChJ</t>
+          <t>Gulshan Tikuv XK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>360721766</t>
+          <t>372941021</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000575634495001</t>
+          <t>20208000028894586001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №118/26, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №194/26, QQS bilan</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1655027000</v>
+        <v>681444000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>164313000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>68480000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Nukus Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>294163528</t>
+          <t>290637122</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000654959719001</t>
+          <t>20208000796179819001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №4/26</t>
+          <t>Shartnoma №284/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1490714000</v>
+        <v>749924000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>53311000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>23454000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Gulshan Tikuv XK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>372941021</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000028894586001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4848 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №9004</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1544025000</v>
+        <v>726470000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>138523000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>54624000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Barakali Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №4278</t>
+          <t>Mahsulot uchun to'lo, shartn. №147/26, QQS 12%</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1405502000</v>
+        <v>781094000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>180798000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>36310000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mehnat Meva-Sabzavot AJ</t>
+          <t>Barakali Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>340425218</t>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000614387330001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №63/26 от 07.09.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №293/26, QQS 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1224704000</v>
+        <v>817404000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>13945000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>28338000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №285/26 от 08.09.2026</t>
+          <t>Materiallar uchun odindan to'lov, shartnoma №189/26</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1238649000</v>
+        <v>789066000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>14776000</v>
+        <v>47912000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Denov Qurilish MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>319956591</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000954561008001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №90/22</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №231/26</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1223873000</v>
+        <v>741154000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>188792000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>615957000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>211538321</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000644053308001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №161/26 от 08.09.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №294/26, QQS 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1035081000</v>
+        <v>1357111000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>142277000</v>
+        <v>47566000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Namangan Metall MChJ</t>
+          <t>Farovon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>325377855</t>
+          <t>272176695</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000036890559001</t>
+          <t>20208000563449540001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4371,37 +4376,37 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №3/26 от 09.09.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №39/26, QQS 12%</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1177358000</v>
+        <v>1404677000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>36230000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>22272000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Ishonch Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>253832106</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000405330890001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4411,197 +4416,192 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №6186</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1213588000</v>
+        <v>1382405000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>27286000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>31567000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
+          <t>Shodlik Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>361215869</t>
+          <t>391344936</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>20208000287406485001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №158/26 от 09.09.2026</t>
+          <t>Оплата за сырье по дог. №110/26 от 07.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1240874000</v>
+        <v>1350838000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>12880000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>138523000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>387662098</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №145/26, НДС 12%</t>
+          <t>Avgust oyi uchun ish haqi, reestr №2058</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1253754000</v>
+        <v>1212315000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>168637000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>14776000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Farovon Ip-Kalava MChJ</t>
+          <t>Olmaliq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>302586059</t>
+          <t>368763789</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000787315931001</t>
+          <t>20208000417526975001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №127/26, QQS 12%</t>
+          <t>Аренда помещения за сентябрь, дог. №13/22</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1422391000</v>
+        <v>1197539000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>396249000</v>
+        <v>37951000</v>
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Buxoro Non AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>294163528</t>
+          <t>216352846</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000654959719001</t>
+          <t>20208000495971938001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №223/26</t>
+          <t>Tovarlar uchun to'lov h/f №5242</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1026142000</v>
+        <v>1159588000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>165219000</v>
+        <v>214647000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>361215869</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4611,37 +4611,37 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7696 от 15.09.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №45/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1191361000</v>
+        <v>1374235000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>44101000</v>
+        <v>37238000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4651,91 +4651,91 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №106/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №8270 за поставленный товар</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1235462000</v>
+        <v>1411473000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>18890000</v>
+        <v>21111000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Оплата за товары согласно с/ф №2727</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1216572000</v>
+        <v>1390362000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>18890000</v>
+        <v>35738000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>391344936</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000287406485001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Оплата за сырье по договору №2/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1197682000</v>
+        <v>1354624000</v>
       </c>
     </row>
     <row r="114">
@@ -4746,36 +4746,36 @@
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>38289000</v>
+        <v>18890000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Andijon Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>388677105</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000017094766001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №273/26 от 15.09.2026, НДС 12%</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1159393000</v>
+        <v>1335734000</v>
       </c>
     </row>
     <row r="115">
@@ -4786,31 +4786,36 @@
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>180300000</v>
+        <v>18890000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7443)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>16307000372315655417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7443 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>979093000</v>
+        <v>1316844000</v>
       </c>
     </row>
     <row r="116">
@@ -4821,22 +4826,17 @@
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>285701000</v>
+        <v>180300000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Navro'z Mehmonxona XK</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>366876378</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7443)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000841752697001</t>
+          <t>16307000372315655417</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4846,117 +4846,117 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №241/26</t>
+          <t>Kredit shartnomasi L-2024-7443 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>693392000</v>
+        <v>1136544000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>23766000</v>
+        <v>20106000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tong Ip-Kalava MChJ</t>
+          <t>Namangan Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>360721766</t>
+          <t>337785570</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000575634495001</t>
+          <t>20208000689055904001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №693 за поставленный товар</t>
+          <t>Shartnoma №205/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>717158000</v>
+        <v>1156650000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>14280000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>92236000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Gulshan Tikuv XK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>372941021</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000028894586001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №216/26 от 16.09.2026</t>
+          <t>Tovarlar uchun to'lov h/f №5995</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>731438000</v>
+        <v>1064414000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>143755000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>183657000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4966,37 +4966,37 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №82/26</t>
+          <t>Shartnoma №204/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>587683000</v>
+        <v>1248071000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>84515000</v>
+        <v>46809000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shodlik Meva Eksport MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>361215869</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000325388208001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5006,331 +5006,331 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №46/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №143/26, QQS 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>672198000</v>
+        <v>1294880000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>48665000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>24430000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shodlik Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>391344936</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000287406485001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7941 от 18.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8185</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>720863000</v>
+        <v>1270450000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>60597000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>29862000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bunyodkor Non MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>388513325</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000936873944001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №279/26</t>
+          <t>Предоплата за товар по договору №38/26 от 23.09.2026</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>660266000</v>
+        <v>1300312000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>81180000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>23960000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5284 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>741446000</v>
+        <v>1276352000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>23499000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>61860000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №285/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №145/26</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>764945000</v>
+        <v>1214492000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>23901000</v>
+        <v>171376000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Gulshan Tikuv XK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>372941021</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000028894586001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Xom ashyo uchun to'lov, shartn. №92/26, QQS bilan</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>741044000</v>
+        <v>1043116000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>17473000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>21145000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Buxoro Non AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>216352846</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000495971938001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3348 от 22.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №14/26, QQS bilan</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>758517000</v>
+        <v>1021971000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>32883000</v>
+        <v>523999000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Shahrisabz Non MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №42/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №144/26, QQS bilan</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>725634000</v>
+        <v>497972000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>66343000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>52590000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Namangan Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>337785570</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000689055904001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №179/26 от 23.09.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №289/26, QQS 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>659291000</v>
+        <v>550562000</v>
       </c>
     </row>
     <row r="129">
@@ -5342,21 +5342,21 @@
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>55486000</v>
+        <v>37408000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon MChJ</t>
+          <t>Shahrisabz Yog'och XK</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>321806655</t>
+          <t>366209842</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000967953442001</t>
+          <t>20208000525711178001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5366,91 +5366,91 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1277 за поставленный товар</t>
+          <t>Tovar uchun to'lov, h/f №1371 25.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>714777000</v>
+        <v>587970000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>20873000</v>
+        <v>83415000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Barakali Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5882 за поставленный товар</t>
+          <t>Shartnoma №280/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>735650000</v>
+        <v>671385000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>47465000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>76650000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Afrosiyob Poligraf MChJ</t>
+          <t>Barakali Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>376729410</t>
+          <t>280665529</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000170288945001</t>
+          <t>20208000795344254001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №213/26</t>
+          <t>Оплата за продукцию по дог. №215/26, НДС 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>688185000</v>
+        <v>748035000</v>
       </c>
     </row>
     <row r="132">
@@ -5462,35 +5462,35 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>24241000</v>
+        <v>67285000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
+          <t>Farovon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>387662098</t>
+          <t>272176695</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>20208000563449540001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5978 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9656 28.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>712426000</v>
+        <v>815320000</v>
       </c>
     </row>
     <row r="133">
@@ -5500,37 +5500,37 @@
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>11105000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>9235000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Namangan Metall MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>325377855</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000036890559001</t>
+          <t>20208000785404252001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6059 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>723531000</v>
+        <v>806085000</v>
       </c>
     </row>
     <row r="134">
@@ -5541,36 +5541,36 @@
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>9235000</v>
+        <v>25914000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Buxoro Non AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>216352846</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000523322308001</t>
+          <t>20208000495971938001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №251/26</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>714296000</v>
+        <v>780171000</v>
       </c>
     </row>
     <row r="135">
@@ -5580,37 +5580,37 @@
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>29308000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>25260000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tong Ip-Kalava MChJ</t>
+          <t>Gulshan Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>360721766</t>
+          <t>367710520</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000575634495001</t>
+          <t>20208000709476643001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7871 29.09.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №56/26</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>743604000</v>
+        <v>754911000</v>
       </c>
     </row>
     <row r="136">
@@ -5620,37 +5620,32 @@
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>12665000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Saodat Avto Ehtiyot AJ</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>387662098</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000215257111001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4145 от 30.09.2026, в т.ч. НДС 12%</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>756269000</v>
+        <v>754611000</v>
       </c>
     </row>
     <row r="137">
@@ -5661,96 +5656,61 @@
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>300000</v>
+        <v>37111000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Shahrisabz Non MChJ</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>335195415</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000236082860001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
+          <t>Xom ashyo uchun to'lov, shartn. №138/26, QQS bilan</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>755969000</v>
+        <v>717500000</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B138" t="n">
-        <v>230</v>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>38469000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Andijon Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>388677105</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>20208000017094766001</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №201/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>717500000</v>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>6696871000</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>6601271000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Итого обороты:</t>
+          <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>6764736000</v>
-      </c>
-      <c r="D139" s="4" t="n">
-        <v>6669136000</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="n">
         <v>717500000</v>
       </c>
-      <c r="D140" s="4" t="n"/>
+      <c r="D139" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
